--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8943,0.0272,0.0579,0.0015</t>
-  </si>
-  <si>
-    <t>0.9300,0.0122,0.0174,0.0041</t>
-  </si>
-  <si>
-    <t>0.9292,0.0206,0.0229,0.0015</t>
-  </si>
-  <si>
-    <t>0.8881,0.0636,0.0121,0.0051</t>
-  </si>
-  <si>
-    <t>0.8211,0.0585,0.0325,0.0174</t>
-  </si>
-  <si>
-    <t>0.7216,0.0715,0.0302,0.0247</t>
-  </si>
-  <si>
-    <t>0.7679,0.0594,0.0490,0.0290</t>
-  </si>
-  <si>
-    <t>0.8828,0.0217,0.0138,0.0185</t>
-  </si>
-  <si>
-    <t>0.8904,0.0536,0.0202,0.0031</t>
-  </si>
-  <si>
-    <t>0.8716,0.0743,0.0212,0.0060</t>
-  </si>
-  <si>
-    <t>0.8072,0.0529,0.0370,0.0192</t>
-  </si>
-  <si>
-    <t>0.5808,0.2136,0.1023,0.0425</t>
-  </si>
-  <si>
-    <t>0.9189,0.0495,0.0214,0.0003</t>
-  </si>
-  <si>
-    <t>0.9563,0.0103,0.0174,0.0007</t>
-  </si>
-  <si>
-    <t>0.8151,0.0157,0.2404,0.0002</t>
-  </si>
-  <si>
-    <t>0.9416,0.0102,0.0415,0.0001</t>
-  </si>
-  <si>
-    <t>0.9540,0.0276,0.0177,0.0004</t>
-  </si>
-  <si>
-    <t>0.4309,0.7080,0.0639,0.0007</t>
-  </si>
-  <si>
-    <t>0.7368,0.2646,0.0724,0.0005</t>
-  </si>
-  <si>
-    <t>0.8170,0.0843,0.0652,0.0078</t>
-  </si>
-  <si>
-    <t>0.0974,0.9349,0.0459,0.0012</t>
-  </si>
-  <si>
-    <t>0.0187,0.9804,0.0725,0.0007</t>
-  </si>
-  <si>
-    <t>0.9522,0.0087,0.0324,0.0002</t>
-  </si>
-  <si>
-    <t>0.9834,0.0028,0.0071,0.0001</t>
-  </si>
-  <si>
-    <t>0.8972,0.0031,0.1379,0.0002</t>
-  </si>
-  <si>
-    <t>0.9396,0.0253,0.0284,0.0005</t>
-  </si>
-  <si>
-    <t>0.9716,0.0045,0.0136,0.0001</t>
-  </si>
-  <si>
-    <t>0.9631,0.0064,0.0240,0.0003</t>
-  </si>
-  <si>
-    <t>0.7861,0.0031,0.3611,0.0004</t>
-  </si>
-  <si>
-    <t>0.2357,0.8000,0.0699,0.0012</t>
-  </si>
-  <si>
-    <t>0.9001,0.0462,0.0181,0.0027</t>
-  </si>
-  <si>
-    <t>0.0295,0.0696,0.9780,0.0014</t>
-  </si>
-  <si>
-    <t>0.5760,0.4590,0.0466,0.0009</t>
-  </si>
-  <si>
-    <t>0.9062,0.0380,0.0159,0.0035</t>
-  </si>
-  <si>
-    <t>0.9124,0.0424,0.0351,0.0010</t>
-  </si>
-  <si>
-    <t>0.8599,0.1170,0.0284,0.0019</t>
-  </si>
-  <si>
-    <t>0.9290,0.0312,0.0281,0.0006</t>
-  </si>
-  <si>
-    <t>0.9575,0.0149,0.0090,0.0005</t>
-  </si>
-  <si>
-    <t>0.9304,0.0032,0.0548,0.0008</t>
-  </si>
-  <si>
-    <t>0.9630,0.0008,0.0404,0.0001</t>
-  </si>
-  <si>
-    <t>0.9279,0.0022,0.0817,0.0004</t>
-  </si>
-  <si>
-    <t>0.9091,0.0030,0.1406,0.0000</t>
-  </si>
-  <si>
-    <t>0.7677,0.0991,0.0606,0.0007</t>
-  </si>
-  <si>
-    <t>0.8836,0.0122,0.0957,0.0020</t>
-  </si>
-  <si>
-    <t>0.8554,0.0892,0.0417,0.0038</t>
-  </si>
-  <si>
-    <t>0.8436,0.1705,0.0286,0.0005</t>
-  </si>
-  <si>
-    <t>0.4919,0.6475,0.0348,0.0002</t>
-  </si>
-  <si>
-    <t>0.8940,0.1285,0.0196,0.0003</t>
-  </si>
-  <si>
-    <t>0.7232,0.0344,0.2248,0.0005</t>
-  </si>
-  <si>
-    <t>0.4195,0.0098,0.7867,0.0001</t>
-  </si>
-  <si>
-    <t>0.9780,0.0014,0.0145,0.0001</t>
-  </si>
-  <si>
-    <t>0.8709,0.0122,0.1313,0.0002</t>
-  </si>
-  <si>
-    <t>0.3852,0.0333,0.7420,0.0005</t>
-  </si>
-  <si>
-    <t>0.7640,0.0116,0.3412,0.0002</t>
-  </si>
-  <si>
-    <t>0.6572,0.1245,0.0671,0.0369</t>
-  </si>
-  <si>
-    <t>0.8824,0.0521,0.0316,0.0033</t>
-  </si>
-  <si>
-    <t>0.8821,0.0334,0.0206,0.0065</t>
-  </si>
-  <si>
-    <t>0.1317,0.5991,0.6577,0.0036</t>
-  </si>
-  <si>
-    <t>0.5460,0.1524,0.0556,0.0405</t>
-  </si>
-  <si>
-    <t>0.7001,0.1229,0.0656,0.0192</t>
-  </si>
-  <si>
-    <t>0.7706,0.0519,0.0323,0.0224</t>
-  </si>
-  <si>
-    <t>0.2857,0.5000,0.2094,0.0002</t>
-  </si>
-  <si>
-    <t>0.5361,0.0371,0.4053,0.0001</t>
-  </si>
-  <si>
-    <t>0.9193,0.0093,0.0744,0.0002</t>
-  </si>
-  <si>
-    <t>0.2221,0.3025,0.5735,0.0003</t>
-  </si>
-  <si>
-    <t>0.5815,0.0012,0.7357,0.0000</t>
-  </si>
-  <si>
-    <t>0.9678,0.0227,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0390,0.9728,0.0227,0.0004</t>
-  </si>
-  <si>
-    <t>0.8803,0.0475,0.0795,0.0012</t>
-  </si>
-  <si>
-    <t>0.7713,0.1523,0.1174,0.0034</t>
-  </si>
-  <si>
-    <t>0.2845,0.0616,0.8143,0.0009</t>
-  </si>
-  <si>
-    <t>0.1429,0.6413,0.2921,0.0004</t>
-  </si>
-  <si>
-    <t>0.8279,0.0808,0.0592,0.0001</t>
-  </si>
-  <si>
-    <t>0.0705,0.9376,0.0523,0.0000</t>
-  </si>
-  <si>
-    <t>0.8218,0.0534,0.0595,0.0001</t>
-  </si>
-  <si>
-    <t>0.9409,0.0151,0.0256,0.0008</t>
-  </si>
-  <si>
-    <t>0.8746,0.0766,0.0291,0.0023</t>
-  </si>
-  <si>
-    <t>0.9666,0.0117,0.0065,0.0007</t>
-  </si>
-  <si>
-    <t>0.9230,0.0450,0.0137,0.0019</t>
-  </si>
-  <si>
-    <t>0.9717,0.0054,0.0086,0.0009</t>
-  </si>
-  <si>
-    <t>0.9768,0.0114,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.8893,0.0216,0.0742,0.0002</t>
-  </si>
-  <si>
-    <t>0.6485,0.0072,0.4745,0.0002</t>
-  </si>
-  <si>
-    <t>0.8664,0.0267,0.1041,0.0003</t>
-  </si>
-  <si>
-    <t>0.9226,0.0069,0.0832,0.0002</t>
-  </si>
-  <si>
-    <t>0.8023,0.0992,0.0583,0.0001</t>
-  </si>
-  <si>
-    <t>0.7195,0.0816,0.1110,0.0003</t>
-  </si>
-  <si>
-    <t>0.8516,0.0589,0.0346,0.0083</t>
-  </si>
-  <si>
-    <t>0.7923,0.0680,0.0373,0.0142</t>
-  </si>
-  <si>
-    <t>0.7660,0.0858,0.0319,0.0103</t>
-  </si>
-  <si>
-    <t>0.8819,0.0263,0.0308,0.0088</t>
-  </si>
-  <si>
-    <t>0.8651,0.0891,0.0361,0.0030</t>
-  </si>
-  <si>
-    <t>0.7615,0.0389,0.0254,0.0456</t>
-  </si>
-  <si>
-    <t>0.7914,0.0776,0.0314,0.0124</t>
-  </si>
-  <si>
-    <t>0.7634,0.0463,0.0327,0.0378</t>
-  </si>
-  <si>
-    <t>0.7157,0.1338,0.0859,0.0167</t>
-  </si>
-  <si>
-    <t>0.7979,0.0585,0.0264,0.0237</t>
-  </si>
-  <si>
-    <t>0.6881,0.0433,0.0191,0.0625</t>
-  </si>
-  <si>
-    <t>0.8315,0.0890,0.0471,0.0071</t>
-  </si>
-  <si>
-    <t>0.7784,0.1052,0.0223,0.0093</t>
-  </si>
-  <si>
-    <t>0.8441,0.0993,0.0394,0.0047</t>
-  </si>
-  <si>
-    <t>0.7655,0.0469,0.0266,0.0277</t>
-  </si>
-  <si>
-    <t>0.8196,0.0679,0.0180,0.0105</t>
-  </si>
-  <si>
-    <t>0.1961,0.0296,0.8886,0.0008</t>
-  </si>
-  <si>
-    <t>0.9615,0.0044,0.0255,0.0001</t>
-  </si>
-  <si>
-    <t>0.9640,0.0125,0.0145,0.0001</t>
-  </si>
-  <si>
-    <t>0.9627,0.0031,0.0282,0.0002</t>
-  </si>
-  <si>
-    <t>0.3843,0.7362,0.0412,0.0014</t>
-  </si>
-  <si>
-    <t>0.6414,0.3292,0.1161,0.0028</t>
-  </si>
-  <si>
-    <t>0.5542,0.4979,0.0858,0.0022</t>
-  </si>
-  <si>
-    <t>0.8342,0.1074,0.0473,0.0019</t>
-  </si>
-  <si>
-    <t>0.6114,0.4496,0.0352,0.0015</t>
-  </si>
-  <si>
-    <t>0.1194,0.9148,0.0445,0.0011</t>
-  </si>
-  <si>
-    <t>0.7023,0.1965,0.0619,0.0068</t>
-  </si>
-  <si>
-    <t>0.9657,0.0124,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.9702,0.0082,0.0112,0.0003</t>
-  </si>
-  <si>
-    <t>0.8294,0.1336,0.0435,0.0012</t>
-  </si>
-  <si>
-    <t>0.9522,0.0179,0.0203,0.0004</t>
-  </si>
-  <si>
-    <t>0.9081,0.0488,0.0418,0.0004</t>
-  </si>
-  <si>
-    <t>0.5560,0.5397,0.0535,0.0003</t>
-  </si>
-  <si>
-    <t>0.8828,0.1318,0.0255,0.0004</t>
-  </si>
-  <si>
-    <t>0.8721,0.2010,0.0123,0.0002</t>
-  </si>
-  <si>
-    <t>0.2765,0.7159,0.1420,0.0008</t>
-  </si>
-  <si>
-    <t>0.8941,0.0855,0.0201,0.0004</t>
-  </si>
-  <si>
-    <t>0.8565,0.0644,0.0506,0.0029</t>
-  </si>
-  <si>
-    <t>0.6813,0.1649,0.1021,0.0177</t>
-  </si>
-  <si>
-    <t>0.8591,0.0509,0.0223,0.0070</t>
-  </si>
-  <si>
-    <t>0.8481,0.0539,0.0398,0.0077</t>
-  </si>
-  <si>
-    <t>0.7556,0.0679,0.0338,0.0330</t>
-  </si>
-  <si>
-    <t>0.7695,0.0562,0.0528,0.0227</t>
-  </si>
-  <si>
-    <t>0.8512,0.0484,0.0304,0.0115</t>
-  </si>
-  <si>
-    <t>0.8506,0.0611,0.0474,0.0082</t>
-  </si>
-  <si>
-    <t>0.6606,0.2470,0.0908,0.0085</t>
-  </si>
-  <si>
-    <t>0.7342,0.0796,0.0706,0.0232</t>
-  </si>
-  <si>
-    <t>0.8437,0.0131,0.1729,0.0002</t>
-  </si>
-  <si>
-    <t>0.8513,0.0091,0.1471,0.0001</t>
-  </si>
-  <si>
-    <t>0.6068,0.0176,0.4335,0.0007</t>
-  </si>
-  <si>
-    <t>0.9121,0.0042,0.1138,0.0001</t>
-  </si>
-  <si>
-    <t>0.9759,0.0055,0.0096,0.0002</t>
-  </si>
-  <si>
-    <t>0.9477,0.0170,0.0286,0.0005</t>
-  </si>
-  <si>
-    <t>0.9593,0.0109,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.9334,0.0288,0.0230,0.0007</t>
-  </si>
-  <si>
-    <t>0.9620,0.0071,0.0118,0.0007</t>
-  </si>
-  <si>
-    <t>0.8874,0.0314,0.0155,0.0089</t>
-  </si>
-  <si>
-    <t>0.9628,0.0132,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.9258,0.0377,0.0187,0.0010</t>
-  </si>
-  <si>
-    <t>0.8795,0.0098,0.1824,0.0003</t>
-  </si>
-  <si>
-    <t>0.8142,0.0771,0.0488,0.0078</t>
-  </si>
-  <si>
-    <t>0.7478,0.1518,0.0407,0.0072</t>
-  </si>
-  <si>
-    <t>0.8419,0.0991,0.0489,0.0038</t>
-  </si>
-  <si>
-    <t>0.7693,0.1172,0.0432,0.0118</t>
-  </si>
-  <si>
-    <t>0.9001,0.0787,0.0220,0.0015</t>
-  </si>
-  <si>
-    <t>0.7731,0.1924,0.0429,0.0028</t>
-  </si>
-  <si>
-    <t>0.7002,0.0751,0.0947,0.0358</t>
-  </si>
-  <si>
-    <t>0.1054,0.2959,0.8879,0.0023</t>
-  </si>
-  <si>
-    <t>0.8507,0.0726,0.0214,0.0086</t>
-  </si>
-  <si>
-    <t>0.8523,0.0618,0.0418,0.0042</t>
-  </si>
-  <si>
-    <t>0.4940,0.5506,0.0672,0.0032</t>
-  </si>
-  <si>
-    <t>0.9337,0.0350,0.0108,0.0017</t>
-  </si>
-  <si>
-    <t>0.8994,0.0410,0.0298,0.0028</t>
-  </si>
-  <si>
-    <t>0.9350,0.0252,0.0281,0.0006</t>
-  </si>
-  <si>
-    <t>0.7959,0.1635,0.0676,0.0012</t>
-  </si>
-  <si>
-    <t>0.8442,0.0991,0.0382,0.0016</t>
-  </si>
-  <si>
-    <t>0.8659,0.0632,0.0223,0.0053</t>
-  </si>
-  <si>
-    <t>0.6619,0.2488,0.1024,0.0070</t>
-  </si>
-  <si>
-    <t>0.7243,0.0732,0.0513,0.0290</t>
-  </si>
-  <si>
-    <t>0.8488,0.0528,0.0396,0.0105</t>
-  </si>
-  <si>
-    <t>0.7850,0.1159,0.0484,0.0094</t>
-  </si>
-  <si>
-    <t>0.7286,0.1149,0.0527,0.0167</t>
-  </si>
-  <si>
-    <t>0.7981,0.0616,0.0516,0.0125</t>
-  </si>
-  <si>
-    <t>0.9673,0.0092,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.8326,0.0896,0.0293,0.0054</t>
-  </si>
-  <si>
-    <t>0.8663,0.0359,0.0242,0.0082</t>
-  </si>
-  <si>
-    <t>0.7838,0.1702,0.0677,0.0040</t>
-  </si>
-  <si>
-    <t>0.9084,0.0435,0.0227,0.0017</t>
-  </si>
-  <si>
-    <t>0.7170,0.1469,0.0981,0.0137</t>
-  </si>
-  <si>
-    <t>0.8573,0.0478,0.0346,0.0068</t>
-  </si>
-  <si>
-    <t>0.9019,0.0183,0.0176,0.0081</t>
-  </si>
-  <si>
-    <t>0.7468,0.1247,0.1039,0.0057</t>
-  </si>
-  <si>
-    <t>0.2421,0.1886,0.7114,0.0024</t>
-  </si>
-  <si>
-    <t>0.8504,0.0552,0.0313,0.0105</t>
-  </si>
-  <si>
-    <t>0.7019,0.0285,0.3346,0.0016</t>
-  </si>
-  <si>
-    <t>0.9414,0.0044,0.0611,0.0001</t>
-  </si>
-  <si>
-    <t>0.8747,0.0310,0.0888,0.0002</t>
-  </si>
-  <si>
-    <t>0.3044,0.0406,0.7155,0.0003</t>
-  </si>
-  <si>
-    <t>0.7871,0.0171,0.2450,0.0004</t>
-  </si>
-  <si>
-    <t>0.8756,0.0176,0.0642,0.0001</t>
-  </si>
-  <si>
-    <t>0.4383,0.0099,0.7389,0.0003</t>
-  </si>
-  <si>
-    <t>0.9417,0.0058,0.0454,0.0002</t>
-  </si>
-  <si>
-    <t>0.9435,0.0185,0.0231,0.0003</t>
-  </si>
-  <si>
-    <t>0.9278,0.0346,0.0277,0.0003</t>
-  </si>
-  <si>
-    <t>0.8550,0.0369,0.1339,0.0004</t>
-  </si>
-  <si>
-    <t>0.9177,0.0389,0.0354,0.0008</t>
-  </si>
-  <si>
-    <t>0.7985,0.0985,0.1100,0.0008</t>
-  </si>
-  <si>
-    <t>0.9530,0.0283,0.0115,0.0004</t>
-  </si>
-  <si>
-    <t>0.8362,0.0770,0.0730,0.0015</t>
-  </si>
-  <si>
-    <t>0.7756,0.1720,0.0615,0.0048</t>
-  </si>
-  <si>
-    <t>0.5007,0.4833,0.0834,0.0059</t>
-  </si>
-  <si>
-    <t>0.8137,0.0862,0.0313,0.0079</t>
-  </si>
-  <si>
-    <t>0.7725,0.1392,0.0318,0.0069</t>
-  </si>
-  <si>
-    <t>0.8147,0.0312,0.0335,0.0192</t>
-  </si>
-  <si>
-    <t>0.8830,0.0809,0.0322,0.0004</t>
-  </si>
-  <si>
-    <t>0.9616,0.0064,0.0231,0.0004</t>
-  </si>
-  <si>
-    <t>0.9688,0.0084,0.0141,0.0003</t>
-  </si>
-  <si>
-    <t>0.9486,0.0145,0.0337,0.0002</t>
-  </si>
-  <si>
-    <t>0.9251,0.0132,0.0365,0.0017</t>
-  </si>
-  <si>
-    <t>0.7708,0.0131,0.3236,0.0002</t>
-  </si>
-  <si>
-    <t>0.9415,0.0069,0.0377,0.0003</t>
-  </si>
-  <si>
-    <t>0.9805,0.0015,0.0111,0.0000</t>
-  </si>
-  <si>
-    <t>0.9780,0.0015,0.0122,0.0000</t>
-  </si>
-  <si>
-    <t>0.8113,0.0091,0.2508,0.0003</t>
-  </si>
-  <si>
-    <t>0.7986,0.0621,0.0324,0.0154</t>
-  </si>
-  <si>
-    <t>0.6878,0.0731,0.0377,0.0441</t>
-  </si>
-  <si>
-    <t>0.8950,0.0183,0.0126,0.0105</t>
-  </si>
-  <si>
-    <t>0.7989,0.0213,0.0085,0.0438</t>
-  </si>
-  <si>
-    <t>0.7397,0.0649,0.0449,0.0369</t>
-  </si>
-  <si>
-    <t>0.7671,0.1003,0.0667,0.0175</t>
-  </si>
-  <si>
-    <t>0.7275,0.0402,0.0216,0.0523</t>
-  </si>
-  <si>
-    <t>0.6498,0.1646,0.0281,0.0161</t>
-  </si>
-  <si>
-    <t>0.9008,0.0189,0.0536,0.0017</t>
-  </si>
-  <si>
-    <t>0.8674,0.0574,0.0409,0.0030</t>
-  </si>
-  <si>
-    <t>0.7647,0.1369,0.0990,0.0042</t>
-  </si>
-  <si>
-    <t>0.8661,0.0039,0.2081,0.0001</t>
-  </si>
-  <si>
-    <t>0.7817,0.0075,0.2364,0.0017</t>
-  </si>
-  <si>
-    <t>0.9463,0.0039,0.0508,0.0001</t>
-  </si>
-  <si>
-    <t>0.7059,0.0007,0.5797,0.0001</t>
-  </si>
-  <si>
-    <t>0.9468,0.0188,0.0231,0.0002</t>
-  </si>
-  <si>
-    <t>0.3864,0.0033,0.7798,0.0005</t>
-  </si>
-  <si>
-    <t>0.9476,0.0058,0.0344,0.0002</t>
-  </si>
-  <si>
-    <t>0.9430,0.0084,0.0403,0.0004</t>
-  </si>
-  <si>
-    <t>0.8997,0.0376,0.0618,0.0003</t>
-  </si>
-  <si>
-    <t>0.9868,0.0030,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9187,0.0202,0.0509,0.0006</t>
-  </si>
-  <si>
-    <t>0.8435,0.1446,0.0384,0.0045</t>
-  </si>
-  <si>
-    <t>0.8649,0.0462,0.0406,0.0046</t>
-  </si>
-  <si>
-    <t>0.8281,0.0376,0.0215,0.0172</t>
-  </si>
-  <si>
-    <t>0.8162,0.0780,0.0330,0.0099</t>
-  </si>
-  <si>
-    <t>0.8012,0.0507,0.0300,0.0202</t>
-  </si>
-  <si>
-    <t>0.7826,0.0898,0.0198,0.0124</t>
-  </si>
-  <si>
-    <t>0.8023,0.1228,0.0353,0.0072</t>
-  </si>
-  <si>
-    <t>0.7852,0.0705,0.0516,0.0196</t>
-  </si>
-  <si>
-    <t>0.9644,0.0023,0.0291,0.0002</t>
-  </si>
-  <si>
-    <t>0.8122,0.0042,0.2799,0.0002</t>
-  </si>
-  <si>
-    <t>0.8339,0.0043,0.2541,0.0001</t>
-  </si>
-  <si>
-    <t>0.9404,0.0239,0.0186,0.0003</t>
-  </si>
-  <si>
-    <t>0.8992,0.0159,0.0730,0.0002</t>
-  </si>
-  <si>
-    <t>0.9716,0.0031,0.0152,0.0001</t>
-  </si>
-  <si>
-    <t>0.9688,0.0037,0.0216,0.0001</t>
-  </si>
-  <si>
-    <t>0.9843,0.0009,0.0050,0.0005</t>
-  </si>
-  <si>
-    <t>0.9110,0.0550,0.0230,0.0011</t>
-  </si>
-  <si>
-    <t>0.9597,0.0164,0.0098,0.0010</t>
-  </si>
-  <si>
-    <t>0.9306,0.0241,0.0135,0.0039</t>
-  </si>
-  <si>
-    <t>0.9204,0.0216,0.0263,0.0024</t>
-  </si>
-  <si>
-    <t>0.9198,0.0149,0.0263,0.0041</t>
-  </si>
-  <si>
-    <t>0.9527,0.0151,0.0089,0.0020</t>
+    <t>0.9534,0.0163,0.0107,0.0090</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.0006,0.9984</t>
+  </si>
+  <si>
+    <t>0.9582,0.0022,0.0027,0.0291</t>
+  </si>
+  <si>
+    <t>0.5131,0.0051,0.0443,0.4459</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9971,0.0002,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9916,0.0043,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9939,0.0021,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9890,0.0023,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.9911,0.0010,0.0005,0.0039</t>
+  </si>
+  <si>
+    <t>0.7186,0.0319,0.2962,0.0037</t>
+  </si>
+  <si>
+    <t>0.1349,0.0156,0.8896,0.0011</t>
+  </si>
+  <si>
+    <t>0.4525,0.0075,0.7452,0.0015</t>
+  </si>
+  <si>
+    <t>0.0321,0.0112,0.9720,0.0018</t>
+  </si>
+  <si>
+    <t>0.9627,0.0135,0.0138,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.9986,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.0022,0.9964,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.1380,0.8727,0.0146,0.0040</t>
+  </si>
+  <si>
+    <t>0.0018,0.9946,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.6439,0.0114,0.4801,0.0071</t>
+  </si>
+  <si>
+    <t>0.4147,0.0288,0.6722,0.0155</t>
+  </si>
+  <si>
+    <t>0.0070,0.0064,0.9900,0.0021</t>
+  </si>
+  <si>
+    <t>0.2114,0.0366,0.7739,0.0259</t>
+  </si>
+  <si>
+    <t>0.1430,0.0033,0.9221,0.0009</t>
+  </si>
+  <si>
+    <t>0.1501,0.0076,0.8648,0.0226</t>
+  </si>
+  <si>
+    <t>0.0026,0.0022,0.9920,0.0070</t>
+  </si>
+  <si>
+    <t>0.2930,0.8311,0.0055,0.0012</t>
+  </si>
+  <si>
+    <t>0.4044,0.0305,0.6680,0.0205</t>
+  </si>
+  <si>
+    <t>0.0021,0.0027,0.9948,0.0035</t>
+  </si>
+  <si>
+    <t>0.0018,0.9852,0.0524,0.0004</t>
+  </si>
+  <si>
+    <t>0.6889,0.1080,0.2142,0.0192</t>
+  </si>
+  <si>
+    <t>0.3305,0.0145,0.8008,0.0034</t>
+  </si>
+  <si>
+    <t>0.5689,0.4742,0.0202,0.0036</t>
+  </si>
+  <si>
+    <t>0.0254,0.9443,0.3465,0.0015</t>
+  </si>
+  <si>
+    <t>0.0404,0.8246,0.4216,0.0175</t>
+  </si>
+  <si>
+    <t>0.0097,0.0064,0.9918,0.0014</t>
+  </si>
+  <si>
+    <t>0.1184,0.0390,0.8953,0.0119</t>
+  </si>
+  <si>
+    <t>0.0121,0.0005,0.9841,0.0050</t>
+  </si>
+  <si>
+    <t>0.0344,0.1761,0.9007,0.0061</t>
+  </si>
+  <si>
+    <t>0.0171,0.9677,0.0140,0.0008</t>
+  </si>
+  <si>
+    <t>0.0111,0.0044,0.9900,0.0008</t>
+  </si>
+  <si>
+    <t>0.3786,0.3213,0.0138,0.3661</t>
+  </si>
+  <si>
+    <t>0.0014,0.9911,0.0036,0.0125</t>
+  </si>
+  <si>
+    <t>0.0003,0.9981,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9977,0.0085,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0377,0.9924,0.0012</t>
+  </si>
+  <si>
+    <t>0.0039,0.1068,0.9926,0.0005</t>
+  </si>
+  <si>
+    <t>0.0421,0.0051,0.9764,0.0014</t>
+  </si>
+  <si>
+    <t>0.0139,0.0032,0.9895,0.0011</t>
+  </si>
+  <si>
+    <t>0.0043,0.0075,0.9919,0.0036</t>
+  </si>
+  <si>
+    <t>0.0085,0.0210,0.9866,0.0028</t>
+  </si>
+  <si>
+    <t>0.9786,0.0177,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9144,0.0345,0.0521,0.0033</t>
+  </si>
+  <si>
+    <t>0.9622,0.0171,0.0092,0.0061</t>
+  </si>
+  <si>
+    <t>0.0054,0.4146,0.9770,0.0052</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9849,0.0104,0.0027,0.0020</t>
+  </si>
+  <si>
+    <t>0.9851,0.0128,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.0006,0.8629,0.9865,0.0001</t>
+  </si>
+  <si>
+    <t>0.0120,0.0574,0.9842,0.0009</t>
+  </si>
+  <si>
+    <t>0.0131,0.0184,0.9847,0.0028</t>
+  </si>
+  <si>
+    <t>0.0004,0.9639,0.9795,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0243,0.9950,0.0008</t>
+  </si>
+  <si>
+    <t>0.0422,0.9644,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.0094,0.9869,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.2532,0.0034,0.8754,0.0077</t>
+  </si>
+  <si>
+    <t>0.0406,0.0434,0.9681,0.0043</t>
+  </si>
+  <si>
+    <t>0.0164,0.0168,0.9827,0.0031</t>
+  </si>
+  <si>
+    <t>0.0038,0.8857,0.8964,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.9704,0.7038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9869,0.1372,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.9763,0.7944,0.0006</t>
+  </si>
+  <si>
+    <t>0.0049,0.0008,0.0480,0.9844</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0038,0.0013,0.0004,0.9984</t>
+  </si>
+  <si>
+    <t>0.0123,0.0030,0.0020,0.9929</t>
+  </si>
+  <si>
+    <t>0.0034,0.0026,0.0038,0.9959</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.9890,0.8961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.1327,0.9850,0.0008</t>
+  </si>
+  <si>
+    <t>0.0047,0.9058,0.2451,0.0032</t>
+  </si>
+  <si>
+    <t>0.0038,0.9148,0.7325,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.9978,0.2611,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.9787,0.1902,0.0012</t>
+  </si>
+  <si>
+    <t>0.9953,0.0012,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9888,0.0059,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9796,0.0162,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9960,0.0017,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0034,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9844,0.0025,0.0014,0.0061</t>
+  </si>
+  <si>
+    <t>0.9932,0.0036,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9895,0.0052,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9950,0.0004,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9942,0.0021,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9882,0.0045,0.0016,0.0025</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0051,0.0025,0.9938,0.0036</t>
+  </si>
+  <si>
+    <t>0.0474,0.0074,0.9773,0.0013</t>
+  </si>
+  <si>
+    <t>0.9689,0.0045,0.0063,0.0085</t>
+  </si>
+  <si>
+    <t>0.0096,0.0006,0.9955,0.0004</t>
+  </si>
+  <si>
+    <t>0.1410,0.8735,0.0065,0.0033</t>
+  </si>
+  <si>
+    <t>0.0057,0.9881,0.0033,0.0024</t>
+  </si>
+  <si>
+    <t>0.0032,0.9921,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.0058,0.9901,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.0009,0.9973,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9966,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.8905,0.1952,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.7727,0.1347,0.0705,0.0178</t>
+  </si>
+  <si>
+    <t>0.0502,0.0115,0.9618,0.0031</t>
+  </si>
+  <si>
+    <t>0.7364,0.0323,0.1675,0.0229</t>
+  </si>
+  <si>
+    <t>0.1431,0.0067,0.9094,0.0043</t>
+  </si>
+  <si>
+    <t>0.0420,0.1239,0.0816,0.8594</t>
+  </si>
+  <si>
+    <t>0.0032,0.9942,0.0197,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9945,0.0039,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.9985,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.0028,0.9714,0.6219,0.0014</t>
+  </si>
+  <si>
+    <t>0.0031,0.9940,0.0252,0.0001</t>
+  </si>
+  <si>
+    <t>0.8157,0.2027,0.0300,0.0027</t>
+  </si>
+  <si>
+    <t>0.8770,0.1310,0.0160,0.0021</t>
+  </si>
+  <si>
+    <t>0.9828,0.0052,0.0050,0.0028</t>
+  </si>
+  <si>
+    <t>0.9956,0.0003,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9852,0.0027,0.0025,0.0037</t>
+  </si>
+  <si>
+    <t>0.9863,0.0040,0.0043,0.0015</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9833,0.0068,0.0041,0.0023</t>
+  </si>
+  <si>
+    <t>0.9870,0.0055,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.9852,0.0009,0.0031,0.0027</t>
+  </si>
+  <si>
+    <t>0.0030,0.9667,0.6623,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.5370,0.9562,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.0072,0.9928,0.0006</t>
+  </si>
+  <si>
+    <t>0.0575,0.0165,0.9643,0.0012</t>
+  </si>
+  <si>
+    <t>0.9772,0.0043,0.0088,0.0010</t>
+  </si>
+  <si>
+    <t>0.8637,0.0051,0.1532,0.0025</t>
+  </si>
+  <si>
+    <t>0.2212,0.0011,0.9342,0.0012</t>
+  </si>
+  <si>
+    <t>0.4641,0.0346,0.6655,0.0044</t>
+  </si>
+  <si>
+    <t>0.0029,0.0003,0.0026,0.9976</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0033,0.0019,0.0007,0.9982</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.0008,0.9988</t>
+  </si>
+  <si>
+    <t>0.0013,0.8482,0.7854,0.0025</t>
+  </si>
+  <si>
+    <t>0.9948,0.0010,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.4325,0.6203,0.0180,0.0161</t>
+  </si>
+  <si>
+    <t>0.9823,0.0035,0.0034,0.0073</t>
+  </si>
+  <si>
+    <t>0.5501,0.4862,0.0135,0.0017</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.7600,0.0032,0.0026,0.3336</t>
+  </si>
+  <si>
+    <t>0.9798,0.0044,0.0016,0.0072</t>
+  </si>
+  <si>
+    <t>0.0028,0.1394,0.9734,0.0206</t>
+  </si>
+  <si>
+    <t>0.7393,0.0001,0.0003,0.5131</t>
+  </si>
+  <si>
+    <t>0.7988,0.0033,0.0013,0.2714</t>
+  </si>
+  <si>
+    <t>0.8739,0.1077,0.0291,0.0039</t>
+  </si>
+  <si>
+    <t>0.9827,0.0071,0.0028,0.0012</t>
+  </si>
+  <si>
+    <t>0.9860,0.0019,0.0045,0.0018</t>
+  </si>
+  <si>
+    <t>0.0829,0.7765,0.1642,0.0288</t>
+  </si>
+  <si>
+    <t>0.8764,0.0494,0.0572,0.0023</t>
+  </si>
+  <si>
+    <t>0.9923,0.0065,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0012,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9940,0.0010,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.9811,0.0030,0.0059,0.0040</t>
+  </si>
+  <si>
+    <t>0.9814,0.0003,0.0004,0.0233</t>
+  </si>
+  <si>
+    <t>0.9912,0.0019,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.9864,0.0022,0.0022,0.0044</t>
+  </si>
+  <si>
+    <t>0.9934,0.0007,0.0006,0.0034</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9397,0.0735,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.8857,0.1380,0.0068,0.0015</t>
+  </si>
+  <si>
+    <t>0.2565,0.7727,0.0149,0.0029</t>
+  </si>
+  <si>
+    <t>0.4177,0.1088,0.6404,0.0102</t>
+  </si>
+  <si>
+    <t>0.9951,0.0012,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9874,0.0036,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9936,0.0029,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9845,0.0040,0.0025,0.0046</t>
+  </si>
+  <si>
+    <t>0.0009,0.0039,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9842,0.0115,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.0084,0.0029,0.9902,0.0036</t>
+  </si>
+  <si>
+    <t>0.0705,0.0162,0.9381,0.0072</t>
+  </si>
+  <si>
+    <t>0.1991,0.0044,0.8789,0.0031</t>
+  </si>
+  <si>
+    <t>0.0006,0.1235,0.9921,0.0018</t>
+  </si>
+  <si>
+    <t>0.0043,0.0185,0.9935,0.0006</t>
+  </si>
+  <si>
+    <t>0.0226,0.0016,0.9822,0.0047</t>
+  </si>
+  <si>
+    <t>0.0071,0.0237,0.9886,0.0012</t>
+  </si>
+  <si>
+    <t>0.2395,0.0065,0.8541,0.0103</t>
+  </si>
+  <si>
+    <t>0.3761,0.0055,0.7878,0.0010</t>
+  </si>
+  <si>
+    <t>0.3004,0.2610,0.4458,0.0138</t>
+  </si>
+  <si>
+    <t>0.1627,0.0337,0.8360,0.0072</t>
+  </si>
+  <si>
+    <t>0.2663,0.0270,0.7998,0.0074</t>
+  </si>
+  <si>
+    <t>0.6010,0.0158,0.4479,0.0050</t>
+  </si>
+  <si>
+    <t>0.5656,0.1407,0.3374,0.0292</t>
+  </si>
+  <si>
+    <t>0.0969,0.0057,0.9608,0.0018</t>
+  </si>
+  <si>
+    <t>0.0227,0.9749,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0405,0.9637,0.0029,0.0011</t>
+  </si>
+  <si>
+    <t>0.7908,0.3192,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.7493,0.3699,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.4597,0.6608,0.0045,0.0027</t>
+  </si>
+  <si>
+    <t>0.9260,0.0109,0.0447,0.0033</t>
+  </si>
+  <si>
+    <t>0.9679,0.0022,0.0218,0.0010</t>
+  </si>
+  <si>
+    <t>0.9050,0.0049,0.0251,0.0354</t>
+  </si>
+  <si>
+    <t>0.9137,0.0046,0.1083,0.0007</t>
+  </si>
+  <si>
+    <t>0.7452,0.0284,0.2273,0.0123</t>
+  </si>
+  <si>
+    <t>0.0178,0.0033,0.9888,0.0009</t>
+  </si>
+  <si>
+    <t>0.0954,0.0592,0.8502,0.0447</t>
+  </si>
+  <si>
+    <t>0.0812,0.0102,0.9283,0.0111</t>
+  </si>
+  <si>
+    <t>0.0037,0.0012,0.9927,0.0027</t>
+  </si>
+  <si>
+    <t>0.0144,0.3773,0.8388,0.0025</t>
+  </si>
+  <si>
+    <t>0.9949,0.0003,0.0001,0.0030</t>
+  </si>
+  <si>
+    <t>0.9629,0.0281,0.0105,0.0044</t>
+  </si>
+  <si>
+    <t>0.9545,0.0417,0.0016,0.0041</t>
+  </si>
+  <si>
+    <t>0.9838,0.0110,0.0023,0.0033</t>
+  </si>
+  <si>
+    <t>0.9794,0.0093,0.0019,0.0055</t>
+  </si>
+  <si>
+    <t>0.9912,0.0039,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9882,0.0036,0.0015,0.0035</t>
+  </si>
+  <si>
+    <t>0.9966,0.0005,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0715,0.0062,0.9720,0.0028</t>
+  </si>
+  <si>
+    <t>0.2342,0.6443,0.2339,0.0268</t>
+  </si>
+  <si>
+    <t>0.9175,0.0141,0.0624,0.0084</t>
+  </si>
+  <si>
+    <t>0.0299,0.0047,0.9808,0.0013</t>
+  </si>
+  <si>
+    <t>0.0041,0.0021,0.9759,0.0402</t>
+  </si>
+  <si>
+    <t>0.0048,0.4247,0.8714,0.0025</t>
+  </si>
+  <si>
+    <t>0.0135,0.0037,0.9914,0.0006</t>
+  </si>
+  <si>
+    <t>0.0653,0.0206,0.9404,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.0029,0.9968,0.0017</t>
+  </si>
+  <si>
+    <t>0.0096,0.0023,0.9891,0.0060</t>
+  </si>
+  <si>
+    <t>0.2373,0.2199,0.3930,0.0246</t>
+  </si>
+  <si>
+    <t>0.9255,0.0030,0.0578,0.0050</t>
+  </si>
+  <si>
+    <t>0.8805,0.0031,0.1495,0.0018</t>
+  </si>
+  <si>
+    <t>0.9539,0.0016,0.0068,0.0211</t>
+  </si>
+  <si>
+    <t>0.9919,0.0046,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0010,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9903,0.0043,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.9913,0.0045,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0016,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9948,0.0018,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0228,0.0455,0.9570,0.0077</t>
+  </si>
+  <si>
+    <t>0.0034,0.0720,0.9855,0.0004</t>
+  </si>
+  <si>
+    <t>0.1480,0.0167,0.8265,0.0036</t>
+  </si>
+  <si>
+    <t>0.0220,0.0149,0.9498,0.0100</t>
+  </si>
+  <si>
+    <t>0.0146,0.0010,0.9857,0.0021</t>
+  </si>
+  <si>
+    <t>0.0415,0.0034,0.9595,0.0160</t>
+  </si>
+  <si>
+    <t>0.3120,0.0070,0.8607,0.0015</t>
+  </si>
+  <si>
+    <t>0.0154,0.0019,0.9243,0.0616</t>
+  </si>
+  <si>
+    <t>0.7032,0.0014,0.0068,0.3584</t>
+  </si>
+  <si>
+    <t>0.0126,0.0130,0.0013,0.9903</t>
+  </si>
+  <si>
+    <t>0.0717,0.0003,0.0017,0.9760</t>
+  </si>
+  <si>
+    <t>0.0027,0.0006,0.0015,0.9976</t>
+  </si>
+  <si>
+    <t>0.0040,0.0002,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.9299,0.0093,0.0185,0.0230</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
